--- a/src/src/main/webapp/portal/budget/TemporallyPurchase/excel/APM_Budget_BAY_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/budget/TemporallyPurchase/excel/APM_Budget_BAY_Exp_Template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\budget\TemporallyPurchase\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\budget\application\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2C1EF2-628D-4468-93D4-B1721E970D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D44345-C4DC-4A81-AD10-B87328DF227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="临时采购申请" sheetId="1" r:id="rId1"/>
+    <sheet name="年度采购申请" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>设备名称</t>
   </si>
@@ -39,9 +39,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>编号</t>
-  </si>
-  <si>
     <t>院区</t>
   </si>
   <si>
@@ -51,9 +48,6 @@
     <t>申请科室</t>
   </si>
   <si>
-    <t>设备品类</t>
-  </si>
-  <si>
     <t>推荐品牌</t>
   </si>
   <si>
@@ -78,7 +72,55 @@
     <t>经费来源</t>
   </si>
   <si>
-    <t>审批时间</t>
+    <t>科室现有同类设备数量</t>
+  </si>
+  <si>
+    <t>科室现有同类设备利用情况</t>
+  </si>
+  <si>
+    <t>是否采购进口产品</t>
+  </si>
+  <si>
+    <t>申购仪器设备的主要功能</t>
+  </si>
+  <si>
+    <t>申购仪器设备的配置</t>
+  </si>
+  <si>
+    <t>申购仪器设备的主要技术参数及要求</t>
+  </si>
+  <si>
+    <t>申购仪器设备在本单位医疗、教学、科研工作中的利用</t>
+  </si>
+  <si>
+    <t>同类产品比较</t>
+  </si>
+  <si>
+    <t>使用年限</t>
+  </si>
+  <si>
+    <t>收费标准</t>
+  </si>
+  <si>
+    <t>年预估收入</t>
+  </si>
+  <si>
+    <t>所需耗材及使用量</t>
+  </si>
+  <si>
+    <t>设备是否有放置场地</t>
+  </si>
+  <si>
+    <t>是否在手术室使用</t>
+  </si>
+  <si>
+    <t>是否需要同院内信息系统对接</t>
+  </si>
+  <si>
+    <t>是否需要连接外网</t>
+  </si>
+  <si>
+    <t>情况说明</t>
   </si>
   <si>
     <t>审批意见</t>
@@ -90,54 +132,153 @@
     <t>记录人</t>
   </si>
   <si>
-    <t>需求说明</t>
+    <t>预算详情</t>
+  </si>
+  <si>
+    <t>预算设备详情</t>
+  </si>
+  <si>
+    <t>线下审批意见</t>
+  </si>
+  <si>
+    <t>申请编号</t>
+  </si>
+  <si>
+    <t>年份</t>
   </si>
   <si>
     <t>申请人</t>
   </si>
   <si>
-    <t>申请理由</t>
-  </si>
-  <si>
-    <t>拟购设备的用途</t>
+    <t>申请日期</t>
+  </si>
+  <si>
+    <t>设备分类</t>
+  </si>
+  <si>
+    <t>社会,经济效益分析</t>
+  </si>
+  <si>
+    <t>护士长是否已签名</t>
+  </si>
+  <si>
+    <t>步骤</t>
+  </si>
+  <si>
+    <t>审批时间(YYYY/MM/DD)</t>
+  </si>
+  <si>
+    <t>审批数量</t>
+  </si>
+  <si>
+    <t>审批单价</t>
+  </si>
+  <si>
+    <t>审批总价</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF172B4D"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF172B4D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -160,19 +301,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{412009C4-6680-4736-BE96-15AD28238389}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -188,7 +394,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -484,95 +690,238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:AS2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.47265625" customWidth="1"/>
-    <col min="17" max="17" width="14.37890625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.47265625" customWidth="1"/>
-    <col min="19" max="21" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.578125" customWidth="1"/>
+    <col min="2" max="2" width="7.5234375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="12.3125" customWidth="1"/>
+    <col min="5" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5234375" customWidth="1"/>
+    <col min="9" max="9" width="11.62890625" customWidth="1"/>
+    <col min="10" max="10" width="12.05078125" customWidth="1"/>
+    <col min="11" max="11" width="5.20703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.62890625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.89453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.41796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.47265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="34.3125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="51.20703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.47265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.15625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.41796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.47265625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.41796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="27.89453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.41796875" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="9" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.20703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.1015625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="15.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:45" ht="18.3">
+      <c r="A1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
+    </row>
+    <row r="2" spans="1:45">
+      <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AA2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="AB2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="AC2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AR2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS2" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <mergeCells count="3">
+    <mergeCell ref="H1:AK1"/>
+    <mergeCell ref="AL1:AS1"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/budget/TemporallyPurchase/excel/APM_Budget_BAY_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/budget/TemporallyPurchase/excel/APM_Budget_BAY_Exp_Template.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\budget\application\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\budget\TemporallyPurchase\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D44345-C4DC-4A81-AD10-B87328DF227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56A2892-5150-4502-BA1A-B9D2561C5185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="年度采购申请" sheetId="1" r:id="rId1"/>
+    <sheet name="临时采购申请" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
